--- a/templates/BulkListingPro-template.xlsx
+++ b/templates/BulkListingPro-template.xlsx
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="197">
   <si>
     <t>sku</t>
   </si>
@@ -389,7 +389,7 @@
 - Printable on US Letter &amp; A4</t>
   </si>
   <si>
-    <t>Planners &amp; Templates</t>
+    <t>Planner Templates</t>
   </si>
   <si>
     <t>I did</t>
@@ -473,10 +473,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Digital Prints</t>
-  </si>
-  <si>
-    <t>Wall art, printable artwork</t>
+    <t>Digital</t>
+  </si>
+  <si>
+    <t>Digital art, illustrations, wall art (Art &amp; Collectibles &gt; Drawing &amp; Illustration &gt; Digital)</t>
   </si>
   <si>
     <t>Guides &amp; How Tos</t>
@@ -485,19 +485,13 @@
     <t>eBooks, tutorials, instructional guides</t>
   </si>
   <si>
-    <t>Drawing &amp; Illustration</t>
-  </si>
-  <si>
-    <t>Digital art, illustrations, drawings</t>
-  </si>
-  <si>
     <t>Digital Patterns</t>
   </si>
   <si>
     <t>Sewing, knitting, crochet patterns</t>
   </si>
   <si>
-    <t>Daily, weekly, monthly planners and templates</t>
+    <t>Daily, weekly, monthly planner templates</t>
   </si>
   <si>
     <t>Clip Art &amp; Image Files</t>
@@ -506,7 +500,7 @@
     <t>Clipart, PNG bundles, graphic elements</t>
   </si>
   <si>
-    <t>Cutting Machine Files (SVG)</t>
+    <t>Cutting Machine Files</t>
   </si>
   <si>
     <t>SVG files for Cricut, Silhouette</t>
@@ -731,7 +725,7 @@
     <t>5.99</t>
   </si>
   <si>
-    <t>Select from dropdown (see Categories sheet)</t>
+    <t>Must match an Etsy taxonomy LEAF exactly. If unsure, type your term into Etsy's "Find a category" search and copy the bottom of the breadcrumb shown.</t>
   </si>
   <si>
     <t>Who made this product? (select from dropdown)</t>
@@ -795,6 +789,15 @@
   </si>
   <si>
     <t>Save as draft or publish? (select from dropdown)</t>
+  </si>
+  <si>
+    <t>--- CATEGORIES ---</t>
+  </si>
+  <si>
+    <t>Etsy taxonomy:</t>
+  </si>
+  <si>
+    <t>Etsy requires the most-specific (leaf) category name. The Categories sheet lists common digital-product leaves, but Etsy can rename or remove them at any time. If a listing fails on category, type the name into Etsy's "Find a category" search and copy the leaf shown at the end of the breadcrumb.</t>
   </si>
   <si>
     <t>--- FILE PATHS ---</t>
@@ -3044,10 +3047,10 @@
       <formula1>0.2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Category" error="Please select a category from the dropdown list." sqref="E10:E501">
-      <formula1>Categories!$A$2:$A$25</formula1>
+      <formula1>Categories!$A$2:$A$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Category" error="Please select a category from the dropdown list." sqref="E2:E501">
-      <formula1>Categories!$A$2:$A$25</formula1>
+      <formula1>Categories!$A$2:$A$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Selection" error="Please select from the dropdown." sqref="F10:F501">
       <formula1>"I did,A member of my shop,Another company or person"</formula1>
@@ -3088,7 +3091,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -3129,15 +3132,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
@@ -3285,14 +3288,6 @@
       </c>
       <c r="B24" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3315,16 +3310,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>63</v>
@@ -3332,7 +3327,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -3344,7 +3339,7 @@
         <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3355,7 +3350,7 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -3372,7 +3367,7 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
         <v>59</v>
@@ -3383,7 +3378,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -3395,7 +3390,7 @@
         <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3406,7 +3401,7 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>59</v>
@@ -3417,7 +3412,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -3429,7 +3424,7 @@
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3440,7 +3435,7 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
         <v>59</v>
@@ -3451,7 +3446,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -3463,7 +3458,7 @@
         <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3474,7 +3469,7 @@
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
         <v>59</v>
@@ -3491,7 +3486,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -3508,7 +3503,7 @@
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -3525,7 +3520,7 @@
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -3536,7 +3531,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -3548,7 +3543,7 @@
         <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3559,7 +3554,7 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
@@ -3570,7 +3565,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
@@ -3582,7 +3577,7 @@
         <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,7 +3588,7 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>59</v>
@@ -3610,7 +3605,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3622,19 +3617,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>63</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -3642,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" t="s">
         <v>140</v>
-      </c>
-      <c r="C2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" t="s">
-        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>59</v>
@@ -3659,13 +3654,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
         <v>143</v>
-      </c>
-      <c r="C3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" t="s">
-        <v>145</v>
       </c>
       <c r="E3" t="s">
         <v>59</v>
@@ -3676,13 +3671,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
         <v>59</v>
@@ -3693,13 +3688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
         <v>59</v>
@@ -3710,16 +3705,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3727,10 +3722,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
@@ -3744,10 +3739,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
         <v>38</v>
@@ -3761,10 +3756,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -3778,10 +3773,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
@@ -3795,13 +3790,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
         <v>59</v>
@@ -3809,13 +3804,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -3829,13 +3824,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
         <v>59</v>
@@ -3846,13 +3841,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
@@ -3860,16 +3855,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" t="s">
         <v>163</v>
-      </c>
-      <c r="B15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" t="s">
-        <v>165</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
@@ -3880,13 +3875,13 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
         <v>59</v>
@@ -3897,16 +3892,16 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3914,10 +3909,10 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>60</v>
@@ -3931,10 +3926,10 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
@@ -3945,31 +3940,44 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>173</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C25" t="s">
         <v>175</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="C26" t="s">
         <v>177</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>178</v>
+      </c>
+      <c r="C27" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3989,18 +3997,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4008,7 +4016,7 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4016,7 +4024,7 @@
         <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4024,15 +4032,15 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4040,7 +4048,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4048,7 +4056,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4056,15 +4064,15 @@
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4072,7 +4080,7 @@
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4080,7 +4088,7 @@
         <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4088,7 +4096,7 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/templates/BulkListingPro-template.xlsx
+++ b/templates/BulkListingPro-template.xlsx
@@ -6,9 +6,10 @@
   <sheets>
     <sheet sheetId="1" name="Products" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Categories" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Options" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Instructions" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="File Paths Help" state="visible" r:id="rId8"/>
+    <sheet sheetId="3" name="Translations" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Options" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Instructions" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="File Paths Help" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -262,6 +263,68 @@
         </r>
       </text>
     </comment>
+    <comment ref="AH1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Optional. Comma-separated ISO codes for translations to upload.
+Valid: nl, fr, de, it, ja, pl, pt, ru, es, sv
+Example: de,fr,it
+Fill the matching rows on the Translations sheet.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0">
+      <text>
+        <r>
+          <t>DELETE THIS ROW - it is just an example</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>One row per (listing × language). Match SKU to a row in the Products sheet.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>ISO 639-1 lowercase code. Valid: nl, fr, de, it, ja, pl, pt, ru, es, sv</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Translated title. Max 140 characters.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>Translated description.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>Tags 1-13. Max 30 chars each (Etsy allows 30 for non-English tags vs 20 for English).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A2" authorId="0">
       <text>
         <r>
@@ -274,7 +337,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="226">
   <si>
     <t>sku</t>
   </si>
@@ -373,6 +436,9 @@
   </si>
   <si>
     <t>listing_state</t>
+  </si>
+  <si>
+    <t>translate_languages</t>
   </si>
   <si>
     <t>PLAN-2026-001</t>
@@ -608,6 +674,61 @@
     <t>Stock photos, photo bundles</t>
   </si>
   <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>2026 Tagesplaner Druckbar PDF - Minimalistischer Stundenplan mit Wochenzielen und Habit Tracker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bleiben Sie das ganze Jahr organisiert mit diesem schönen 2026 Tagesplaner!
+Enthalten:
+- 365 Tagesplaner-Seiten
+- 52 Wochenübersichten
+- 12 Monatsübersichten</t>
+  </si>
+  <si>
+    <t>tagesplaner druckbar</t>
+  </si>
+  <si>
+    <t>digitaler kalender 2026</t>
+  </si>
+  <si>
+    <t>planer pdf druckbar</t>
+  </si>
+  <si>
+    <t>goodnotes vorlage</t>
+  </si>
+  <si>
+    <t>habit tracker deutsch</t>
+  </si>
+  <si>
+    <t>stundenplan pdf</t>
+  </si>
+  <si>
+    <t>minimalistischer planer</t>
+  </si>
+  <si>
+    <t>ipad kalender vorlage</t>
+  </si>
+  <si>
+    <t>sofort download</t>
+  </si>
+  <si>
+    <t>wochenziele tracker</t>
+  </si>
+  <si>
+    <t>pdf planer 2026</t>
+  </si>
+  <si>
+    <t>produktivität pdf</t>
+  </si>
+  <si>
+    <t>digitaler download</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -791,6 +912,12 @@
     <t>Save as draft or publish? (select from dropdown)</t>
   </si>
   <si>
+    <t>Comma-separated ISO codes. Add matching rows on the Translations sheet.</t>
+  </si>
+  <si>
+    <t>de,fr,it</t>
+  </si>
+  <si>
     <t>--- CATEGORIES ---</t>
   </si>
   <si>
@@ -798,6 +925,33 @@
   </si>
   <si>
     <t>Etsy requires the most-specific (leaf) category name. The Categories sheet lists common digital-product leaves, but Etsy can rename or remove them at any time. If a listing fails on category, type the name into Etsy's "Find a category" search and copy the leaf shown at the end of the breadcrumb.</t>
+  </si>
+  <si>
+    <t>--- TRANSLATIONS ---</t>
+  </si>
+  <si>
+    <t>translate_languages:</t>
+  </si>
+  <si>
+    <t>Comma-separated ISO codes (de,fr,it). Determines which languages to upload for each listing.</t>
+  </si>
+  <si>
+    <t>Translations sheet:</t>
+  </si>
+  <si>
+    <t>One row per (listing × language). Match SKU to the Products sheet. Fill title, description, and up to 13 tags per row.</t>
+  </si>
+  <si>
+    <t>Tag character limit:</t>
+  </si>
+  <si>
+    <t>Etsy allows 30 chars for non-English tags (vs 20 for English). Use this to your advantage.</t>
+  </si>
+  <si>
+    <t>Auto-translate:</t>
+  </si>
+  <si>
+    <t>Or skip the Translations sheet — use the Translate button in the editor. 1 credit per listing for all checked languages.</t>
   </si>
   <si>
     <t>--- FILE PATHS ---</t>
@@ -1300,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG501"/>
+  <dimension ref="A1:AH501"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1317,9 +1471,10 @@
     <col min="30" max="30" width="30" customWidth="1"/>
     <col min="31" max="31" width="10" customWidth="1"/>
     <col min="32" max="33" width="14" customWidth="1"/>
+    <col min="34" max="34" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="25" customHeight="1" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1419,102 +1574,108 @@
       <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="5">
         <v>4.99</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AE2" s="4">
         <v>999</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
@@ -3100,194 +3261,194 @@
   <sheetData>
     <row r="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3297,6 +3458,1150 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q1001"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="5" max="17" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="201" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="202" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="210" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="211" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="212" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="213" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="214" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="215" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="216" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="217" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="218" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="219" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="220" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="221" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="222" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="223" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="224" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="225" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="226" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="227" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="228" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="229" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="230" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="231" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="232" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="233" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="235" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="236" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="237" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="238" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="239" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="240" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="241" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="242" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="243" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="244" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="245" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="246" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="248" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="250" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="254" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="259" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="273" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="274" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="275" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="276" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="277" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="278" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="279" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="280" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="281" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="282" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="283" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="284" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="285" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="286" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="287" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="288" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="289" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="290" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="291" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="292" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="293" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="294" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="295" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="296" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="297" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="298" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="299" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="301" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="303" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="304" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="305" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="306" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="310" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="312" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="313" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="314" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="315" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="316" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="317" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="318" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="319" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="320" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="321" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="322" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="323" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="324" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="325" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="326" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="327" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="328" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="329" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="330" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="331" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="337" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="338" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="339" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="340" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="342" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="343" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="344" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="345" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="346" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="347" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="348" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="349" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="350" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="351" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="352" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="353" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="354" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="355" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="356" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="357" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="358" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="359" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="360" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="361" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="362" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="363" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="364" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="365" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="366" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="367" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="368" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="369" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="370" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="372" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="373" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="374" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="375" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="376" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="377" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="378" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="379" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="380" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="381" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="382" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="383" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="384" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="386" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="387" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="388" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="389" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="390" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="391" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="392" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="393" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="394" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="395" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="396" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="397" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="399" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="401" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="402" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="403" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="404" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="405" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="406" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="407" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="408" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="409" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="410" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="411" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="412" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="413" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="414" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="415" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="416" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="417" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="418" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="419" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="420" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="421" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="432" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="433" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="434" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="435" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="436" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="437" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="438" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="439" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="440" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="441" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="442" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="443" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="444" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="445" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="446" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="447" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="448" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="449" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="450" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="451" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="452" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="453" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="454" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="455" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="456" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="457" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="458" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="459" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="460" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="461" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="462" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="463" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="464" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="465" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="466" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="467" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="468" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="469" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="470" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="471" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="472" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="473" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="475" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="476" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="477" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="478" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="479" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="480" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="481" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="482" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="483" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="484" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="485" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="486" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="487" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="488" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="489" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="490" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="491" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="492" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="493" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="494" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="497" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="498" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="499" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="500" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="501" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="502" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="503" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="504" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="505" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="506" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="507" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="508" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="509" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="510" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="511" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="512" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="513" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="514" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="515" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="516" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="517" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="518" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="519" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="520" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="521" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="522" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="523" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="524" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="525" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="526" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="527" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="528" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="529" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="530" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="531" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="532" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="533" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="534" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="535" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="536" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="537" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="538" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="539" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="540" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="541" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="542" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="543" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="544" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="545" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="546" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="547" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="548" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="549" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="550" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="551" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="552" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="553" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="554" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="555" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="556" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="557" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="558" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="559" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="560" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="561" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="562" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="563" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="564" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="565" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="566" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="567" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="568" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="569" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="570" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="571" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="572" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="573" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="574" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="575" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="576" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="577" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="578" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="579" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="580" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="581" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="582" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="583" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="584" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="585" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="586" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="587" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="588" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="589" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="590" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="591" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="592" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="593" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="594" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="595" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="596" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="597" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="598" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="599" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="600" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="601" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="602" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="603" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="604" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="605" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="606" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="607" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="608" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="609" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="610" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="611" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="612" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="613" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="614" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="615" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="616" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="617" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="618" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="619" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="620" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="621" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="622" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="623" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="624" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="625" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="626" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="627" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="628" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="629" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="630" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="631" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="632" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="633" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="634" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="635" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="636" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="637" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="638" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="639" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="640" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="641" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="642" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="643" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="644" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="645" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="646" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="647" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="648" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="649" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="650" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="651" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="652" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="653" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="654" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="655" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="656" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="657" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="658" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="659" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="660" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="661" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="662" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="663" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="664" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="665" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="666" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="667" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="668" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="669" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="670" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="671" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="672" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="673" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="674" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="675" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="676" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="677" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="678" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="679" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="680" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="681" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="682" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="683" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="684" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="685" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="686" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="687" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="688" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="689" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="690" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="691" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="692" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="693" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="694" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="695" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="696" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="697" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="698" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="699" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="700" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="701" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="702" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="703" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="704" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="705" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="706" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="707" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="708" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="709" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="710" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="711" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="712" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="713" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="714" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="715" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="716" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="717" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="718" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="719" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="720" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="721" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="722" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="723" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="724" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="725" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="726" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="727" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="728" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="729" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="730" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="731" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="732" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="733" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="734" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="735" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="736" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="737" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="738" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="739" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="740" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="741" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="742" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="743" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="744" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="745" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="746" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="747" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="748" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="749" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="750" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="751" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="752" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="753" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="754" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="755" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="756" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="757" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="758" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="759" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="760" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="761" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="762" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="763" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="764" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="765" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="766" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="767" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="768" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="769" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="770" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="771" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="772" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="773" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="774" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="775" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="776" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="777" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="778" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="779" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="780" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="781" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="782" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="783" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="784" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="785" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="786" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="787" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="788" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="789" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="790" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="791" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="792" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="793" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="794" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="795" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="796" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="797" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="798" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="799" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="800" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="801" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="802" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="803" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="804" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="805" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="806" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="807" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="808" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="809" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="810" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="811" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="812" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="813" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="814" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="815" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="816" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="817" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="818" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="819" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="820" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="821" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="822" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="823" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="824" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="825" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="826" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="827" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="828" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="829" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="830" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="831" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="832" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="833" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="834" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="835" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="836" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="837" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="838" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="839" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="840" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="841" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="842" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="843" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="844" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="845" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="846" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="847" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="848" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="849" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="850" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="851" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="852" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="853" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="854" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="855" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="856" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="857" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="858" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="859" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="860" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="861" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="862" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="863" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="864" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="865" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="866" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="867" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="868" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="869" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="870" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="871" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="872" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="873" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="874" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="875" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="876" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="877" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="878" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="879" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="880" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="881" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="882" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="883" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="884" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="885" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="886" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="887" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="888" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="889" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="890" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="891" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="892" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="893" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="894" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="895" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="896" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="897" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="898" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="899" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="900" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="901" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="902" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="903" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="904" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="905" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="906" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="907" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="908" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="909" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="910" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="911" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="912" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="913" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="914" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="915" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="916" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="917" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="918" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="919" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="920" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="921" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="922" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="923" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="924" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="925" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="926" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="927" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="928" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="929" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="930" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="931" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="932" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="933" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="934" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="935" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="936" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="937" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="938" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="939" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="940" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="941" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="942" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="943" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="944" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="945" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="946" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="947" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="948" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="949" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="950" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="951" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="952" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="953" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="954" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="955" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="956" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="957" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="958" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="959" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="960" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="961" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="962" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="963" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="964" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="965" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="966" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="967" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="968" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="969" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="970" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="971" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="972" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="973" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="974" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="975" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="976" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="977" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="978" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="979" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="980" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="981" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="982" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="983" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="984" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="985" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="986" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="987" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="988" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="989" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="990" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="991" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="992" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="993" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="994" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="995" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="996" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="997" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="998" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="999" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="1000" spans="2:17" x14ac:dyDescent="0.25"/>
+    <row r="1001" spans="2:17" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Language" error="Use a 2-letter ISO code: nl, fr, de, it, ja, pl, pt, ru, es, sv" sqref="B10:B1001">
+      <formula1>"nl,fr,de,it,ja,pl,pt,ru,es,sv"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Language" error="Use a 2-letter ISO code: nl, fr, de, it, ja, pl, pt, ru, es, sv" sqref="B2:B1001">
+      <formula1>"nl,fr,de,it,ja,pl,pt,ru,es,sv"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Title Too Long" error="Translated title must be 140 characters or fewer." sqref="C10:C1001">
+      <formula1>140</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Title Too Long" error="Translated title must be 140 characters or fewer." sqref="C2:C1001">
+      <formula1>140</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Tag Too Long" error="Each translated tag must be 30 characters or fewer." sqref="E10:Q1001">
+      <formula1>30</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Tag Too Long" error="Each translated tag must be 30 characters or fewer." sqref="E2:Q1001">
+      <formula1>30</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3310,291 +4615,291 @@
   <sheetData>
     <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3603,9 +4908,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3617,19 +4922,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -3637,16 +4942,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3654,16 +4959,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -3671,16 +4976,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -3688,16 +4993,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -3705,16 +5010,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3722,16 +5027,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,16 +5044,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3756,16 +5061,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3773,16 +5078,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3790,33 +5095,33 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3824,16 +5129,16 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -3841,33 +5146,33 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -3875,16 +5180,16 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3892,16 +5197,16 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3909,16 +5214,16 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3926,58 +5231,112 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="C27" t="s">
-        <v>179</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>205</v>
+      </c>
+      <c r="C33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3986,7 +5345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3997,106 +5356,106 @@
   <sheetData>
     <row r="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
